--- a/evaluation/connectivity_evaluation.xlsx
+++ b/evaluation/connectivity_evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frederick\Desktop\masters\trento_QCB\03_semester\knowledge_graphs\project\Oncovirus-Knowledge-Graph\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773B6745-DE2C-48E0-ABB8-833D5E05D8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973656E1-F185-4517-ACBD-9171FD469B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
